--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2378,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124186807</v>
+        <v>124186456</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,37 +2394,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495978</v>
+        <v>495968</v>
       </c>
       <c r="R17" t="n">
-        <v>6927274</v>
+        <v>6927228</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2490,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186456</v>
+        <v>124186807</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,46 +2515,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495968</v>
+        <v>495978</v>
       </c>
       <c r="R18" t="n">
-        <v>6927228</v>
+        <v>6927274</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124186525</v>
+        <v>124186456</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,41 +2278,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495964</v>
+        <v>495968</v>
       </c>
       <c r="R16" t="n">
-        <v>6927248</v>
+        <v>6927228</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124186456</v>
+        <v>124186525</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,50 +2399,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495968</v>
+        <v>495964</v>
       </c>
       <c r="R17" t="n">
-        <v>6927228</v>
+        <v>6927248</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124186456</v>
+        <v>124186807</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,46 +2282,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495968</v>
+        <v>495978</v>
       </c>
       <c r="R16" t="n">
-        <v>6927228</v>
+        <v>6927274</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2499,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186807</v>
+        <v>124186456</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,37 +2506,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495978</v>
+        <v>495968</v>
       </c>
       <c r="R18" t="n">
-        <v>6927274</v>
+        <v>6927228</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124186807</v>
+        <v>124186456</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,37 +2282,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495978</v>
+        <v>495968</v>
       </c>
       <c r="R16" t="n">
-        <v>6927274</v>
+        <v>6927228</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124186525</v>
+        <v>124186807</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495964</v>
+        <v>495978</v>
       </c>
       <c r="R17" t="n">
-        <v>6927248</v>
+        <v>6927274</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2490,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186456</v>
+        <v>124186525</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,50 +2511,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495968</v>
+        <v>495964</v>
       </c>
       <c r="R18" t="n">
-        <v>6927228</v>
+        <v>6927248</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124186456</v>
+        <v>124186525</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,50 +2278,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495968</v>
+        <v>495964</v>
       </c>
       <c r="R16" t="n">
-        <v>6927228</v>
+        <v>6927248</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2499,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186525</v>
+        <v>124186456</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,41 +2502,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495964</v>
+        <v>495968</v>
       </c>
       <c r="R18" t="n">
-        <v>6927248</v>
+        <v>6927228</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124186525</v>
+        <v>124186456</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,41 +2278,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495964</v>
+        <v>495968</v>
       </c>
       <c r="R16" t="n">
-        <v>6927248</v>
+        <v>6927228</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124186807</v>
+        <v>124186525</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495978</v>
+        <v>495964</v>
       </c>
       <c r="R17" t="n">
-        <v>6927274</v>
+        <v>6927248</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2490,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124186456</v>
+        <v>124186807</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,46 +2515,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gillbergstjärnarna, Gillbergstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495968</v>
+        <v>495978</v>
       </c>
       <c r="R18" t="n">
-        <v>6927228</v>
+        <v>6927274</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 44607-2021 artfynd.xlsx
+++ b/artfynd/A 44607-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111408063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474368</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124186807</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111488192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111488254</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111667765</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111668233</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111422433</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474119</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111667755</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124186525</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474642</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474182</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2207,6 +2277,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124186456</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111423664</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2423,6 +2503,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474444</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111667775</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2639,8 +2729,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>